--- a/panel-proyectos/data/DATOS_MIXTOS.xlsx
+++ b/panel-proyectos/data/DATOS_MIXTOS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\MIXTOS_APP\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CN594\Downloads\CPEL_APP (1)\panel-proyectos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B8F785-211D-46C4-ABC4-4FD5FBCD03A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42059F0F-F21B-49A6-91BE-E23E1BA0FBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Proyectos" sheetId="1" r:id="rId1"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Proyectos!$A$1:$Q$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="347">
   <si>
     <t>NO.</t>
   </si>
@@ -849,15 +852,6 @@
     <t>55.50%</t>
   </si>
   <si>
-    <t>87.50%</t>
-  </si>
-  <si>
-    <t>67.00%</t>
-  </si>
-  <si>
-    <t>83.40%</t>
-  </si>
-  <si>
     <t>76.00%</t>
   </si>
   <si>
@@ -879,27 +873,12 @@
     <t>75.50%</t>
   </si>
   <si>
-    <t>28.00%</t>
-  </si>
-  <si>
     <t>66.00%</t>
   </si>
   <si>
-    <t>67.25%</t>
-  </si>
-  <si>
-    <t>59.40%</t>
-  </si>
-  <si>
-    <t>67.50%</t>
-  </si>
-  <si>
     <t>59.00%</t>
   </si>
   <si>
-    <t>65.80%</t>
-  </si>
-  <si>
     <t>37.50%</t>
   </si>
   <si>
@@ -936,15 +915,6 @@
     <t>52.80%</t>
   </si>
   <si>
-    <t>82.75%</t>
-  </si>
-  <si>
-    <t>71.25%</t>
-  </si>
-  <si>
-    <t>80.45%</t>
-  </si>
-  <si>
     <t>60.50%</t>
   </si>
   <si>
@@ -1090,6 +1060,24 @@
   </si>
   <si>
     <t>76.60%</t>
+  </si>
+  <si>
+    <t>83.00%</t>
+  </si>
+  <si>
+    <t>73.50%</t>
+  </si>
+  <si>
+    <t>80.70%</t>
+  </si>
+  <si>
+    <t>65.40%</t>
+  </si>
+  <si>
+    <t>85.50%</t>
+  </si>
+  <si>
+    <t>86.30%</t>
   </si>
 </sst>
 </file>
@@ -1581,13 +1569,13 @@
         <v>238</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>18</v>
@@ -1634,13 +1622,13 @@
         <v>239</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>270</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>20</v>
@@ -1687,13 +1675,13 @@
         <v>240</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>20</v>
@@ -1740,13 +1728,13 @@
         <v>241</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>273</v>
+        <v>346</v>
       </c>
       <c r="Q5" s="6" t="s">
         <v>18</v>
@@ -1793,16 +1781,16 @@
         <v>242</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -1846,13 +1834,13 @@
         <v>243</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q7" s="6" t="s">
         <v>20</v>
@@ -1899,13 +1887,13 @@
         <v>244</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>20</v>
@@ -1952,13 +1940,13 @@
         <v>245</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>282</v>
+        <v>344</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>20</v>
@@ -2005,13 +1993,13 @@
         <v>246</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>20</v>
@@ -2058,16 +2046,16 @@
         <v>247</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>20</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2111,13 +2099,13 @@
         <v>248</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>20</v>
@@ -2164,16 +2152,16 @@
         <v>249</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2217,13 +2205,13 @@
         <v>250</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>20</v>
@@ -2270,13 +2258,13 @@
         <v>251</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="Q15" s="6" t="s">
         <v>20</v>
@@ -2323,13 +2311,13 @@
         <v>252</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="Q16" s="6" t="s">
         <v>20</v>
@@ -2376,13 +2364,13 @@
         <v>253</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>20</v>
@@ -2429,16 +2417,16 @@
         <v>254</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2482,13 +2470,13 @@
         <v>255</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="Q19" s="6" t="s">
         <v>20</v>
@@ -2535,13 +2523,13 @@
         <v>256</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="Q20" s="6" t="s">
         <v>20</v>
@@ -2588,13 +2576,13 @@
         <v>257</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>20</v>
@@ -2641,13 +2629,13 @@
         <v>258</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>270</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>20</v>
@@ -2694,13 +2682,13 @@
         <v>259</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>18</v>
@@ -2747,13 +2735,13 @@
         <v>260</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>20</v>
@@ -2800,13 +2788,13 @@
         <v>261</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>20</v>
@@ -2853,13 +2841,13 @@
         <v>262</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>20</v>
@@ -2906,16 +2894,16 @@
         <v>263</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -2959,13 +2947,13 @@
         <v>264</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q28" s="6" t="s">
         <v>20</v>
@@ -3012,16 +3000,16 @@
         <v>265</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3065,16 +3053,16 @@
         <v>266</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -3118,13 +3106,13 @@
         <v>267</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="Q31" s="6" t="s">
         <v>18</v>
@@ -3171,13 +3159,13 @@
         <v>172</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>20</v>
@@ -3224,13 +3212,13 @@
         <v>268</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>20</v>
@@ -3277,13 +3265,13 @@
         <v>172</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="Q34" s="6" t="s">
         <v>20</v>
@@ -3330,13 +3318,13 @@
         <v>172</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>20</v>
@@ -3383,13 +3371,13 @@
         <v>172</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="Q36" s="6" t="s">
         <v>20</v>
@@ -3436,13 +3424,13 @@
         <v>172</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>20</v>
@@ -3489,13 +3477,13 @@
         <v>172</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="Q38" s="6" t="s">
         <v>20</v>
@@ -3542,20 +3530,25 @@
         <v>172</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:Q1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q39">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
